--- a/clodoo/clodoo/transodoo.xlsx
+++ b/clodoo/clodoo/transodoo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="859">
   <si>
     <t xml:space="preserve">model</t>
   </si>
@@ -2519,6 +2519,18 @@
   </si>
   <si>
     <t xml:space="preserve">zip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_supplier</t>
   </si>
   <si>
     <t xml:space="preserve">res.users</t>
@@ -11058,35 +11070,37 @@
     </row>
     <row r="539" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B539" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D539" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="B539" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D539" s="1" t="s">
+      <c r="E539" s="3"/>
+      <c r="M539" s="1" t="s">
         <v>834</v>
-      </c>
-      <c r="E539" s="3" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="3" t="s">
-        <v>833</v>
+        <v>192</v>
       </c>
       <c r="B540" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D540" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="E540" s="3"/>
+      <c r="M540" s="1" t="s">
         <v>836</v>
-      </c>
-      <c r="E540" s="3" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="3" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B541" s="3" t="s">
         <v>27</v>
@@ -11100,85 +11114,85 @@
     </row>
     <row r="542" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="3" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B542" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="D542" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="E542" s="3" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
     </row>
     <row r="543" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="3" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B543" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="D543" s="1" t="s">
+        <v>842</v>
+      </c>
       <c r="E543" s="3" t="s">
-        <v>93</v>
+        <v>843</v>
       </c>
     </row>
     <row r="544" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B544" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D544" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="G544" s="3" t="s">
-        <v>842</v>
+        <v>27</v>
+      </c>
+      <c r="E544" s="3" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="545" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B545" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D545" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H545" s="1" t="s">
-        <v>132</v>
+      <c r="E545" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="546" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B546" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C546" s="1" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>719</v>
+        <v>845</v>
+      </c>
+      <c r="G546" s="3" t="s">
+        <v>846</v>
       </c>
     </row>
     <row r="547" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C547" s="1" t="s">
-        <v>163</v>
+        <v>27</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>739</v>
+        <v>131</v>
+      </c>
+      <c r="H547" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B548" s="3" t="s">
         <v>33</v>
@@ -11187,12 +11201,12 @@
         <v>163</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>736</v>
+        <v>719</v>
       </c>
     </row>
     <row r="549" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B549" s="3" t="s">
         <v>33</v>
@@ -11201,15 +11215,12 @@
         <v>163</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="G549" s="3" t="s">
-        <v>144</v>
+        <v>739</v>
       </c>
     </row>
     <row r="550" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B550" s="3" t="s">
         <v>33</v>
@@ -11218,15 +11229,12 @@
         <v>163</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>844</v>
-      </c>
-      <c r="G550" s="3" t="s">
-        <v>144</v>
+        <v>736</v>
       </c>
     </row>
     <row r="551" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B551" s="3" t="s">
         <v>33</v>
@@ -11235,7 +11243,7 @@
         <v>163</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="G551" s="3" t="s">
         <v>144</v>
@@ -11243,7 +11251,7 @@
     </row>
     <row r="552" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B552" s="3" t="s">
         <v>33</v>
@@ -11252,12 +11260,15 @@
         <v>163</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>742</v>
+        <v>848</v>
+      </c>
+      <c r="G552" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="553" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B553" s="3" t="s">
         <v>33</v>
@@ -11266,7 +11277,7 @@
         <v>163</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="G553" s="3" t="s">
         <v>144</v>
@@ -11274,7 +11285,7 @@
     </row>
     <row r="554" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B554" s="3" t="s">
         <v>33</v>
@@ -11283,26 +11294,29 @@
         <v>163</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="G554" s="3" t="s">
-        <v>144</v>
+        <v>742</v>
       </c>
     </row>
     <row r="555" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="3" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="C555" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
+      </c>
+      <c r="G555" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="3" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B556" s="3" t="s">
         <v>33</v>
@@ -11311,29 +11325,26 @@
         <v>163</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>719</v>
+        <v>851</v>
+      </c>
+      <c r="G556" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="557" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="3" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C557" s="1" t="s">
-        <v>163</v>
+        <v>27</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="H557" s="1" t="s">
-        <v>144</v>
+        <v>853</v>
       </c>
     </row>
     <row r="558" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="3" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B558" s="3" t="s">
         <v>33</v>
@@ -11342,12 +11353,12 @@
         <v>163</v>
       </c>
       <c r="D558" s="1" t="s">
-        <v>739</v>
+        <v>719</v>
       </c>
     </row>
     <row r="559" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="3" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B559" s="3" t="s">
         <v>33</v>
@@ -11356,12 +11367,15 @@
         <v>163</v>
       </c>
       <c r="D559" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
+      </c>
+      <c r="H559" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="560" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="3" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B560" s="3" t="s">
         <v>33</v>
@@ -11370,50 +11384,76 @@
         <v>163</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="H560" s="1" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="561" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="3" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="C561" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>852</v>
+        <v>736</v>
       </c>
     </row>
     <row r="562" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="C562" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>136</v>
+        <v>854</v>
+      </c>
+      <c r="H562" s="1" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B563" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D563" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="564" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A564" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="B564" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D564" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="565" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A565" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="B565" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D565" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="G563" s="3" t="s">
+      <c r="G565" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/clodoo/clodoo/transodoo.xlsx
+++ b/clodoo/clodoo/transodoo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2459" uniqueCount="868">
   <si>
     <t xml:space="preserve">model</t>
   </si>
@@ -730,6 +730,9 @@
     <t xml:space="preserve">discuss.channel</t>
   </si>
   <si>
+    <t xml:space="preserve">message_edit[</t>
+  </si>
+  <si>
     <t xml:space="preserve">sale.quote.option</t>
   </si>
   <si>
@@ -1033,6 +1036,9 @@
     <t xml:space="preserve">account_full_reconcile</t>
   </si>
   <si>
+    <t xml:space="preserve">account_usability</t>
+  </si>
+  <si>
     <t xml:space="preserve">account_invoice_reorder_lines</t>
   </si>
   <si>
@@ -1132,6 +1138,9 @@
     <t xml:space="preserve">l10n_it_fatturapa_in</t>
   </si>
   <si>
+    <t xml:space="preserve">l10n_it_edi_extension</t>
+  </si>
+  <si>
     <t xml:space="preserve">l10n_it_fatturapa_in_improved</t>
   </si>
   <si>
@@ -1510,6 +1519,9 @@
     <t xml:space="preserve">l10n_it_central_journal</t>
   </si>
   <si>
+    <t xml:space="preserve">l10n_it_central_journal_reportlab</t>
+  </si>
+  <si>
     <t xml:space="preserve">account_check_writing</t>
   </si>
   <si>
@@ -1724,6 +1736,9 @@
   </si>
   <si>
     <t xml:space="preserve">l10n_it_ricevute_bancarie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l10n_it_riba_oca</t>
   </si>
   <si>
     <t xml:space="preserve">account_banking_riba</t>
@@ -2902,7 +2917,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB566"/>
+  <dimension ref="A1:AB567"/>
   <sheetFormatPr defaultColWidth="27.01953125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.01"/>
@@ -5427,11 +5442,11 @@
       <c r="B153" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D153" s="1" t="s">
+      <c r="H153" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="J153" s="1" t="s">
-        <v>237</v>
+      <c r="P153" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5442,10 +5457,10 @@
         <v>0</v>
       </c>
       <c r="D154" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J154" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5456,10 +5471,10 @@
         <v>0</v>
       </c>
       <c r="D155" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J155" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="J155" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5470,10 +5485,10 @@
         <v>0</v>
       </c>
       <c r="D156" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J156" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="I156" s="3" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5484,358 +5499,358 @@
         <v>0</v>
       </c>
       <c r="D157" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="I157" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="I157" s="3" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I158" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="T158" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F159" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="T159" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="T159" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F160" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="T160" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="T160" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F161" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="T161" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="T161" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F162" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="T162" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="T162" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F163" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="T163" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="T163" s="1" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F164" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="T164" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="T164" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F165" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="T165" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="T165" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F166" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="T166" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="T166" s="1" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F167" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="T167" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="T167" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F168" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="T168" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="T168" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F169" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="T169" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="T169" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F170" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="T170" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="T170" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F171" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="T171" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="T171" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F172" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="T172" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="T172" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F173" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="T173" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="T173" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F174" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="T174" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="T174" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F175" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="T175" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="T175" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F176" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="T176" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="T176" s="1" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D177" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="T177" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>288</v>
@@ -5843,248 +5858,242 @@
     </row>
     <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D179" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F179" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D180" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F180" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="G180" s="3" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D181" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G181" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="G181" s="3" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D182" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G182" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D183" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G183" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="G183" s="3" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D184" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G184" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G184" s="3"/>
-      <c r="H184" s="2"/>
-      <c r="I184" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="J184" s="2"/>
     </row>
     <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G185" s="3"/>
       <c r="H185" s="2"/>
       <c r="I185" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J185" s="2"/>
     </row>
     <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D186" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G186" s="3"/>
+      <c r="H186" s="2"/>
+      <c r="I186" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="G186" s="3"/>
-      <c r="J186" s="1" t="s">
-        <v>304</v>
-      </c>
+      <c r="J186" s="2"/>
     </row>
     <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G187" s="3"/>
       <c r="J187" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D188" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G188" s="3"/>
+      <c r="J188" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="J188" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D189" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J189" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="J189" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D190" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="J190" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="J190" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D191" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="J191" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="G191" s="3"/>
-      <c r="J191" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G192" s="3"/>
       <c r="J192" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G193" s="3"/>
       <c r="J193" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G194" s="3"/>
+      <c r="J194" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="B194" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H194" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="Z194" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="AB194" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>190</v>
@@ -6093,60 +6102,66 @@
         <v>80</v>
       </c>
       <c r="H195" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="Z195" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="Z195" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="AB195" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D196" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="Z196" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="G196" s="3" t="s">
-        <v>325</v>
+      <c r="AB196" s="1" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D197" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G197" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D198" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G198" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="J198" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>190</v>
@@ -6154,13 +6169,13 @@
       <c r="D199" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="G199" s="3" t="s">
-        <v>327</v>
+      <c r="J199" s="1" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>190</v>
@@ -6169,12 +6184,12 @@
         <v>330</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>190</v>
@@ -6183,43 +6198,43 @@
         <v>331</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="J201" s="1" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D202" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J202" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="G202" s="3" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D203" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G203" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="H203" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>190</v>
@@ -6227,83 +6242,86 @@
       <c r="D204" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="G204" s="3" t="s">
-        <v>327</v>
+      <c r="H204" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="P204" s="1" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="J205" s="1" t="s">
-        <v>327</v>
+        <v>339</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="H206" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
+      </c>
+      <c r="J206" s="1" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="G207" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D208" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="G208" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="G208" s="3" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>190</v>
@@ -6317,7 +6335,7 @@
     </row>
     <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>190</v>
@@ -6325,55 +6343,55 @@
       <c r="D211" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="J211" s="1" t="s">
-        <v>327</v>
+      <c r="G211" s="3" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="G212" s="3" t="s">
-        <v>327</v>
+        <v>348</v>
+      </c>
+      <c r="J212" s="1" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>190</v>
@@ -6381,13 +6399,13 @@
       <c r="D215" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="J215" s="1" t="s">
+      <c r="G215" s="3" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>190</v>
@@ -6396,68 +6414,68 @@
         <v>353</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D217" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="J217" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="G217" s="3" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="J219" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="G220" s="3" t="s">
         <v>358</v>
+      </c>
+      <c r="J220" s="1" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>190</v>
@@ -6471,7 +6489,7 @@
     </row>
     <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>190</v>
@@ -6480,40 +6498,40 @@
         <v>361</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>190</v>
@@ -6522,27 +6540,26 @@
         <v>365</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="H226" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="Z226" s="2"/>
+      <c r="G226" s="3" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="227" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>190</v>
@@ -6550,30 +6567,28 @@
       <c r="D227" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G227" s="3" t="s">
-        <v>339</v>
-      </c>
+      <c r="H227" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z227" s="2"/>
     </row>
     <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="Z228" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="AB228" s="1" t="s">
-        <v>370</v>
+      <c r="G228" s="3" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>190</v>
@@ -6581,386 +6596,395 @@
       <c r="D229" s="1" t="s">
         <v>371</v>
       </c>
+      <c r="P229" s="1" t="s">
+        <v>372</v>
+      </c>
       <c r="Z229" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AB229" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F230" s="1" t="s">
         <v>374</v>
+      </c>
+      <c r="P230" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z230" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="AB230" s="1" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y231" s="3" t="s">
         <v>376</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="H232" s="1" t="s">
-        <v>358</v>
+        <v>378</v>
+      </c>
+      <c r="Y232" s="3" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="G234" s="3" t="s">
-        <v>360</v>
+        <v>381</v>
+      </c>
+      <c r="H234" s="1" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="H235" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="G236" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="H237" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="G237" s="3" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G239" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="H239" s="1" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="I242" s="3" t="s">
         <v>394</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="G243" s="3" t="s">
         <v>396</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="I244" s="3" t="s">
-        <v>187</v>
+        <v>398</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="H245" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="G246" s="3" t="s">
         <v>401</v>
+      </c>
+      <c r="H246" s="1" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="H247" s="1" t="s">
         <v>403</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="J249" s="1" t="s">
-        <v>390</v>
+        <v>407</v>
+      </c>
+      <c r="H249" s="1" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="G250" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
+      </c>
+      <c r="J250" s="1" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>145</v>
+        <v>413</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>413</v>
+        <v>145</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>145</v>
+        <v>416</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="J255" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="G255" s="3" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>145</v>
@@ -6968,496 +6992,490 @@
     </row>
     <row r="257" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="H257" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
+      </c>
+      <c r="J257" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>352</v>
+        <v>423</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="G260" s="3" t="s">
-        <v>352</v>
+        <v>424</v>
+      </c>
+      <c r="H260" s="1" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>424</v>
+        <v>354</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="H262" s="1" t="s">
-        <v>394</v>
+        <v>426</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="I263" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
+      </c>
+      <c r="H263" s="1" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="H264" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
+      </c>
+      <c r="I264" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="G265" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
+      </c>
+      <c r="H265" s="1" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D266" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G266" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="G266" s="3" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="J268" s="1" t="s">
-        <v>427</v>
+        <v>434</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J269" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="G270" s="3" t="s">
-        <v>427</v>
+        <v>436</v>
+      </c>
+      <c r="J270" s="1" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="H271" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H274" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="G275" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="H275" s="1" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>382</v>
+        <v>448</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="J279" s="1" t="s">
-        <v>390</v>
+        <v>449</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="G280" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
+      </c>
+      <c r="J280" s="1" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="H281" s="1" t="s">
-        <v>145</v>
+        <v>451</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="G282" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
+      </c>
+      <c r="H282" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="H283" s="1" t="s">
         <v>454</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>455</v>
+        <v>190</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G284" s="3"/>
-      <c r="J284" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="Y284" s="1" t="s">
+      <c r="H284" s="1" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>80</v>
       </c>
       <c r="G285" s="3"/>
       <c r="J285" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Y285" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H286" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="Z286" s="1" t="s">
+      <c r="G286" s="3"/>
+      <c r="J286" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="AB286" s="1" t="s">
-        <v>461</v>
+      <c r="Y286" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="S287" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="W287" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="X287" s="1" t="s">
-        <v>80</v>
+      <c r="Z287" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="AB287" s="1" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
+      </c>
+      <c r="S288" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="W288" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="AA288" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="X288" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="W289" s="3" t="s">
-        <v>80</v>
+        <v>468</v>
       </c>
       <c r="AA289" s="3" t="s">
         <v>80</v>
@@ -7465,41 +7483,38 @@
     </row>
     <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="S290" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="W290" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Z290" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB290" s="1" t="s">
+      <c r="AA290" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="W291" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="S291" s="3" t="s">
         <v>80</v>
       </c>
       <c r="Z291" s="1" t="s">
@@ -7511,2202 +7526,2223 @@
     </row>
     <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="I292" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="W292" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z292" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB292" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J293" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="S293" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z293" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB293" s="1" t="s">
+      <c r="H293" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="I293" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F294" s="1" t="s">
-        <v>345</v>
+      <c r="J294" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="S294" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="Z294" s="1" t="s">
-        <v>471</v>
+        <v>80</v>
       </c>
       <c r="AB294" s="1" t="s">
-        <v>471</v>
+        <v>80</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="G295" s="3" t="s">
-        <v>473</v>
+        <v>80</v>
+      </c>
+      <c r="F295" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="P295" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z295" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="AB295" s="1" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G298" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="H299" s="1" t="s">
         <v>481</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H301" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="I304" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="Y304" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="Z304" s="1" t="s">
-        <v>491</v>
+      <c r="H304" s="1" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I305" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Y305" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z305" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="H306" s="1" t="s">
         <v>495</v>
+      </c>
+      <c r="I306" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="Y306" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="Z306" s="1" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="G307" s="3" t="s">
         <v>497</v>
+      </c>
+      <c r="H307" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="P307" s="1" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="I308" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
+      </c>
+      <c r="G308" s="3" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="G309" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="J309" s="1" t="s">
-        <v>333</v>
+        <v>502</v>
+      </c>
+      <c r="I309" s="3" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="I310" s="3" t="s">
-        <v>327</v>
+        <v>504</v>
+      </c>
+      <c r="G310" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J310" s="1" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="H311" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
+      </c>
+      <c r="I311" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="P311" s="1" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="G313" s="3" t="s">
-        <v>339</v>
+        <v>508</v>
+      </c>
+      <c r="H313" s="1" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>506</v>
+        <v>342</v>
       </c>
       <c r="G314" s="3" t="s">
-        <v>507</v>
+        <v>341</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G315" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="J316" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
+      </c>
+      <c r="G316" s="3" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="G317" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
+      </c>
+      <c r="J317" s="1" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="I318" s="3" t="s">
-        <v>327</v>
+        <v>516</v>
+      </c>
+      <c r="G318" s="3" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="Z319" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="AB319" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
+      </c>
+      <c r="I319" s="3" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="H320" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
+      </c>
+      <c r="Z320" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="AB320" s="1" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="I321" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
+      </c>
+      <c r="H321" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="H322" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
+      </c>
+      <c r="I322" s="3" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H323" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="J324" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
+      </c>
+      <c r="H324" s="1" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="H325" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
+      </c>
+      <c r="J325" s="1" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="G326" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
+      </c>
+      <c r="H326" s="1" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="J327" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
+      </c>
+      <c r="G327" s="3" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J328" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="I329" s="3" t="s">
-        <v>360</v>
+        <v>537</v>
+      </c>
+      <c r="J329" s="1" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="I330" s="3" t="s">
-        <v>537</v>
+        <v>362</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I331" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="G332" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
+      </c>
+      <c r="I332" s="3" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G333" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="H334" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
+      </c>
+      <c r="G334" s="3" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="I335" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
+      </c>
+      <c r="H335" s="1" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="H336" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
+      </c>
+      <c r="I336" s="3" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="I338" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
+      </c>
+      <c r="H338" s="1" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="G339" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
+      </c>
+      <c r="I339" s="3" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I340" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
+      </c>
+      <c r="G340" s="3" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="G341" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
+      </c>
+      <c r="I341" s="3" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="H342" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
+      </c>
+      <c r="G342" s="3" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G343" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
+      </c>
+      <c r="H343" s="1" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="F344" s="1" t="s">
-        <v>374</v>
+        <v>566</v>
+      </c>
+      <c r="G344" s="3" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="W345" s="3" t="s">
-        <v>565</v>
+        <v>568</v>
+      </c>
+      <c r="F345" s="1" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>371</v>
       </c>
       <c r="W346" s="3" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="Z347" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="AB347" s="1" t="s">
-        <v>568</v>
+        <v>374</v>
+      </c>
+      <c r="W347" s="3" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="I348" s="3" t="s">
-        <v>360</v>
+        <v>571</v>
+      </c>
+      <c r="P348" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="Z348" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="AB348" s="1" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="I349" s="3" t="s">
-        <v>571</v>
+        <v>362</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="H350" s="1" t="s">
-        <v>570</v>
+        <v>575</v>
+      </c>
+      <c r="I350" s="3" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="G351" s="3" t="s">
-        <v>574</v>
+        <v>577</v>
+      </c>
+      <c r="H351" s="1" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G352" s="3" t="s">
-        <v>381</v>
+        <v>579</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="I353" s="3" t="s">
-        <v>577</v>
+        <v>580</v>
+      </c>
+      <c r="G353" s="3" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="I354" s="3" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="G355" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
+      </c>
+      <c r="I355" s="3" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G356" s="3" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="H357" s="1" t="s">
-        <v>396</v>
+        <v>587</v>
+      </c>
+      <c r="G357" s="3" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="G358" s="3" t="s">
-        <v>586</v>
+        <v>589</v>
+      </c>
+      <c r="H358" s="1" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="I359" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
+      </c>
+      <c r="G359" s="3" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="I360" s="3" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="G361" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
+      </c>
+      <c r="I361" s="3" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="I362" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
+      </c>
+      <c r="G362" s="3" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="I363" s="3" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="H364" s="1" t="s">
-        <v>344</v>
+        <v>600</v>
+      </c>
+      <c r="I364" s="3" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="G365" s="3" t="s">
-        <v>599</v>
+        <v>602</v>
+      </c>
+      <c r="H365" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="I366" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
+      </c>
+      <c r="G366" s="3" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="I367" s="3" t="s">
-        <v>508</v>
+        <v>606</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="I368" s="3" t="s">
-        <v>145</v>
+        <v>512</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="I369" s="3" t="s">
-        <v>605</v>
+        <v>145</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="G370" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
+      </c>
+      <c r="I370" s="3" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="I371" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
+      </c>
+      <c r="G371" s="3" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="I372" s="3" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="H373" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
+      </c>
+      <c r="I373" s="3" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="J374" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
+      </c>
+      <c r="H374" s="1" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="H375" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
+      </c>
+      <c r="J375" s="1" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="G376" s="3" t="s">
-        <v>618</v>
+        <v>620</v>
+      </c>
+      <c r="H376" s="1" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="G377" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="I378" s="3" t="s">
-        <v>622</v>
+        <v>624</v>
+      </c>
+      <c r="G378" s="3" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="J379" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
+      </c>
+      <c r="I379" s="3" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="G380" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
+      </c>
+      <c r="J380" s="1" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="I381" s="3" t="s">
-        <v>390</v>
+        <v>630</v>
+      </c>
+      <c r="G381" s="3" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>627</v>
+        <v>395</v>
       </c>
       <c r="I382" s="3" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="I383" s="3" t="s">
-        <v>629</v>
+        <v>406</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="H384" s="1" t="s">
-        <v>417</v>
+        <v>633</v>
+      </c>
+      <c r="I384" s="3" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="H385" s="1" t="s">
-        <v>632</v>
+        <v>420</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="G386" s="3" t="s">
-        <v>629</v>
+        <v>636</v>
+      </c>
+      <c r="H386" s="1" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D387" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="G387" s="3" t="s">
         <v>634</v>
-      </c>
-      <c r="G387" s="3" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="G388" s="3" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="G389" s="3" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="I390" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
+      </c>
+      <c r="G390" s="3" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="I391" s="3" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="I392" s="3" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="I393" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>449</v>
+        <v>650</v>
       </c>
       <c r="I394" s="3" t="s">
-        <v>352</v>
+        <v>651</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="H395" s="1" t="s">
-        <v>648</v>
+        <v>452</v>
+      </c>
+      <c r="I395" s="3" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="H396" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="G397" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
+      </c>
+      <c r="H397" s="1" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="G398" s="3" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="H399" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
+      </c>
+      <c r="G399" s="3" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>388</v>
+        <v>660</v>
       </c>
       <c r="H400" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>658</v>
+        <v>391</v>
       </c>
       <c r="H401" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="G402" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
+      </c>
+      <c r="H402" s="1" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="G403" s="3" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="I404" s="3" t="s">
-        <v>145</v>
+        <v>667</v>
+      </c>
+      <c r="G404" s="3" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="I405" s="3" t="s">
-        <v>666</v>
+        <v>145</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="I406" s="3" t="s">
-        <v>641</v>
+        <v>671</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="J407" s="1" t="s">
-        <v>418</v>
+        <v>672</v>
+      </c>
+      <c r="I407" s="3" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="G408" s="3" t="s">
-        <v>670</v>
+        <v>673</v>
+      </c>
+      <c r="J408" s="1" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="I409" s="3" t="s">
-        <v>663</v>
+        <v>674</v>
+      </c>
+      <c r="G409" s="3" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="I410" s="3" t="s">
-        <v>394</v>
+        <v>668</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="I411" s="3" t="s">
-        <v>673</v>
+        <v>397</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="G412" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
+      </c>
+      <c r="I412" s="3" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="I413" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
+      </c>
+      <c r="G413" s="3" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="I414" s="3" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="I415" s="3" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="I416" s="3" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="I417" s="3" t="s">
-        <v>427</v>
+        <v>688</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="H418" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
+      </c>
+      <c r="I418" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="J419" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
+      </c>
+      <c r="H419" s="1" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="G420" s="3" t="s">
-        <v>690</v>
+        <v>692</v>
+      </c>
+      <c r="J420" s="1" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="I421" s="3" t="s">
-        <v>427</v>
+        <v>694</v>
+      </c>
+      <c r="G421" s="3" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="G422" s="3" t="s">
-        <v>693</v>
+        <v>696</v>
+      </c>
+      <c r="I422" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="J423" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
+      </c>
+      <c r="G423" s="3" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="I424" s="3" t="s">
-        <v>697</v>
+        <v>699</v>
+      </c>
+      <c r="J424" s="1" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="G425" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
+      </c>
+      <c r="I425" s="3" t="s">
+        <v>702</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="I426" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
+      </c>
+      <c r="G426" s="3" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="I427" s="3" t="s">
-        <v>416</v>
+        <v>706</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="I428" s="3" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="I429" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I430" s="3" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="J431" s="1" t="s">
-        <v>707</v>
+        <v>710</v>
+      </c>
+      <c r="I431" s="3" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="I432" s="3" t="s">
-        <v>447</v>
+        <v>711</v>
+      </c>
+      <c r="J432" s="1" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="433" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="J433" s="1" t="s">
-        <v>452</v>
+        <v>713</v>
+      </c>
+      <c r="I433" s="3" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B434" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D434" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="J434" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="D434" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="H434" s="1" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="J435" s="1" t="s">
-        <v>454</v>
+        <v>715</v>
+      </c>
+      <c r="H435" s="1" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="436" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="I436" s="3" t="s">
-        <v>701</v>
+        <v>717</v>
+      </c>
+      <c r="J436" s="1" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A437" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="B437" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="H437" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="J437" s="1" t="s">
-        <v>717</v>
+      <c r="A437" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D437" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="I437" s="3" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A438" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="B438" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D438" s="1" t="s">
-        <v>1</v>
+      <c r="A438" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="H438" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="J438" s="1" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F439" s="1" t="s">
-        <v>719</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G440" s="3" t="s">
-        <v>161</v>
+        <v>80</v>
+      </c>
+      <c r="F440" s="1" t="s">
+        <v>724</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
+      </c>
+      <c r="G441" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G442" s="3" t="s">
-        <v>29</v>
+        <v>162</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="G443" s="3" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>164</v>
+        <v>134</v>
+      </c>
+      <c r="G444" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G445" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="s">
-        <v>216</v>
+        <v>725</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="G446" s="3" t="s">
-        <v>86</v>
+        <v>166</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9717,10 +9753,10 @@
         <v>28</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G447" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9731,29 +9767,26 @@
         <v>28</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
+      </c>
+      <c r="G448" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
-        <v>721</v>
+        <v>216</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C449" s="1" t="s">
-        <v>164</v>
+        <v>28</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="J449" s="1" t="s">
-        <v>723</v>
+        <v>156</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>34</v>
@@ -9762,143 +9795,145 @@
         <v>164</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="J450" s="1" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+      <c r="C451" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="G451" s="3"/>
-      <c r="L451" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
+      </c>
+      <c r="J451" s="1" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="G452" s="3"/>
       <c r="L452" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="G453" s="3"/>
       <c r="L453" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="F454" s="1" t="s">
-        <v>2</v>
+        <v>735</v>
+      </c>
+      <c r="G454" s="3"/>
+      <c r="L454" s="1" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="G455" s="3"/>
-      <c r="L455" s="1" t="s">
-        <v>727</v>
+        <v>737</v>
+      </c>
+      <c r="F455" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="G456" s="3"/>
       <c r="L456" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="B457" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D457" s="1" t="s">
         <v>733</v>
-      </c>
-      <c r="B457" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D457" s="1" t="s">
-        <v>730</v>
       </c>
       <c r="G457" s="3"/>
       <c r="L457" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A458" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="B458" s="1" t="s">
+      <c r="A458" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="B458" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D458" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="J458" s="1" t="s">
+      <c r="G458" s="3"/>
+      <c r="L458" s="1" t="s">
         <v>736</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A459" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B459" s="3" t="s">
+      <c r="A459" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B459" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E459" s="2"/>
-      <c r="F459" s="4" t="s">
-        <v>79</v>
+        <v>740</v>
+      </c>
+      <c r="J459" s="1" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9909,11 +9944,11 @@
         <v>28</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E460" s="2"/>
       <c r="F460" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9928,7 +9963,7 @@
       </c>
       <c r="E461" s="2"/>
       <c r="F461" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="462" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9943,7 +9978,7 @@
       </c>
       <c r="E462" s="2"/>
       <c r="F462" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9958,7 +9993,7 @@
       </c>
       <c r="E463" s="2"/>
       <c r="F463" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9973,7 +10008,7 @@
       </c>
       <c r="E464" s="2"/>
       <c r="F464" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="465" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9988,7 +10023,7 @@
       </c>
       <c r="E465" s="2"/>
       <c r="F465" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10003,7 +10038,7 @@
       </c>
       <c r="E466" s="2"/>
       <c r="F466" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10018,7 +10053,7 @@
       </c>
       <c r="E467" s="2"/>
       <c r="F467" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="468" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10033,7 +10068,7 @@
       </c>
       <c r="E468" s="2"/>
       <c r="F468" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10048,7 +10083,7 @@
       </c>
       <c r="E469" s="2"/>
       <c r="F469" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10063,7 +10098,7 @@
       </c>
       <c r="E470" s="2"/>
       <c r="F470" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10078,7 +10113,7 @@
       </c>
       <c r="E471" s="2"/>
       <c r="F471" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10093,7 +10128,7 @@
       </c>
       <c r="E472" s="2"/>
       <c r="F472" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10108,7 +10143,7 @@
       </c>
       <c r="E473" s="2"/>
       <c r="F473" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10123,7 +10158,7 @@
       </c>
       <c r="E474" s="2"/>
       <c r="F474" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10138,7 +10173,7 @@
       </c>
       <c r="E475" s="2"/>
       <c r="F475" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10153,7 +10188,7 @@
       </c>
       <c r="E476" s="2"/>
       <c r="F476" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10168,7 +10203,7 @@
       </c>
       <c r="E477" s="2"/>
       <c r="F477" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10183,7 +10218,7 @@
       </c>
       <c r="E478" s="2"/>
       <c r="F478" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="479" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10198,7 +10233,7 @@
       </c>
       <c r="E479" s="2"/>
       <c r="F479" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10213,7 +10248,7 @@
       </c>
       <c r="E480" s="2"/>
       <c r="F480" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10228,29 +10263,27 @@
       </c>
       <c r="E481" s="2"/>
       <c r="F481" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="482" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A482" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B482" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D482" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E482" s="2"/>
+      <c r="F482" s="4" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="482" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A482" s="3" t="s">
-        <v>737</v>
-      </c>
-      <c r="B482" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C482" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D482" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="G482" s="3" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B483" s="3" t="s">
         <v>34</v>
@@ -10259,15 +10292,15 @@
         <v>164</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="G483" s="3" t="s">
-        <v>740</v>
+        <v>187</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B484" s="3" t="s">
         <v>34</v>
@@ -10276,12 +10309,15 @@
         <v>164</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>723</v>
+        <v>744</v>
+      </c>
+      <c r="G484" s="3" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>34</v>
@@ -10290,15 +10326,12 @@
         <v>164</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="G485" s="3" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>34</v>
@@ -10307,12 +10340,15 @@
         <v>164</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>743</v>
+        <v>746</v>
+      </c>
+      <c r="G486" s="3" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B487" s="3" t="s">
         <v>34</v>
@@ -10321,12 +10357,12 @@
         <v>164</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B488" s="3" t="s">
         <v>34</v>
@@ -10335,15 +10371,12 @@
         <v>164</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="G488" s="3" t="s">
-        <v>187</v>
+        <v>745</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B489" s="3" t="s">
         <v>34</v>
@@ -10352,7 +10385,7 @@
         <v>164</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="G489" s="3" t="s">
         <v>187</v>
@@ -10360,7 +10393,7 @@
     </row>
     <row r="490" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B490" s="3" t="s">
         <v>34</v>
@@ -10369,12 +10402,15 @@
         <v>164</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>746</v>
+        <v>750</v>
+      </c>
+      <c r="G490" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="3" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>34</v>
@@ -10383,12 +10419,12 @@
         <v>164</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>723</v>
+        <v>751</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="3" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>34</v>
@@ -10397,15 +10433,12 @@
         <v>164</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="G492" s="3" t="s">
-        <v>187</v>
+        <v>728</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="3" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>34</v>
@@ -10414,7 +10447,7 @@
         <v>164</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="G493" s="3" t="s">
         <v>187</v>
@@ -10422,7 +10455,7 @@
     </row>
     <row r="494" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="3" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>34</v>
@@ -10431,459 +10464,462 @@
         <v>164</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>740</v>
+        <v>748</v>
+      </c>
+      <c r="G494" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="3" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+      <c r="C495" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="3" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B496" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G496" s="3"/>
-      <c r="H496" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="J496" s="1" t="s">
-        <v>752</v>
+      <c r="D496" s="1" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="3" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G497" s="3"/>
       <c r="H497" s="1" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="J497" s="1" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="3" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="B498" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G498" s="3"/>
       <c r="H498" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="J498" s="1" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="3" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="B499" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G499" s="3"/>
       <c r="H499" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="J499" s="1" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="3" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="B500" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G500" s="3"/>
       <c r="H500" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="J500" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="3" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G501" s="3"/>
       <c r="H501" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="K501" s="1" t="s">
-        <v>80</v>
+        <v>764</v>
+      </c>
+      <c r="J501" s="1" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="3" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="B502" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C502" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="D502" s="1" t="s">
-        <v>764</v>
+        <v>28</v>
+      </c>
+      <c r="G502" s="3"/>
+      <c r="H502" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="K502" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="E503" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="G503" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E504" s="3" t="s">
-        <v>771</v>
+        <v>772</v>
+      </c>
+      <c r="G504" s="3" t="s">
+        <v>773</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="G505" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
+      </c>
+      <c r="E505" s="3" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="F506" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
+      </c>
+      <c r="G506" s="3" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F507" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="H508" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
+      </c>
+      <c r="F508" s="1" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B509" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="F509" s="1" t="s">
-        <v>780</v>
+        <v>787</v>
+      </c>
+      <c r="H509" s="1" t="s">
+        <v>788</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B510" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C510" s="1" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>766</v>
+        <v>790</v>
+      </c>
+      <c r="F510" s="1" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B511" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="E511" s="3" t="s">
-        <v>789</v>
+        <v>771</v>
       </c>
     </row>
     <row r="512" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="E512" s="3" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="G513" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
+      </c>
+      <c r="E513" s="3" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C514" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="E514" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
+      </c>
+      <c r="G514" s="3" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B515" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E515" s="3" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B516" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="E516" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="H516" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B517" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="F517" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
+      </c>
+      <c r="E517" s="3" t="s">
+        <v>809</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B518" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C518" s="1" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="E518" s="3" t="s">
-        <v>811</v>
+        <v>778</v>
+      </c>
+      <c r="F518" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="H518" s="1" t="s">
+        <v>813</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B519" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E519" s="3"/>
-      <c r="G519" s="4" t="s">
-        <v>812</v>
-      </c>
-      <c r="H519" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="520" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C519" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="D519" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="E519" s="3" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="520" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B520" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E520" s="3"/>
       <c r="G520" s="4" t="s">
-        <v>814</v>
-      </c>
-      <c r="H520" s="4" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="521" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>817</v>
+      </c>
+      <c r="H520" s="1" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="521" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B521" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E521" s="3"/>
-      <c r="G521" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="H521" s="1" t="s">
-        <v>817</v>
+      <c r="G521" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="H521" s="4" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="3" t="s">
-        <v>193</v>
+        <v>767</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D522" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="G522" s="3" t="s">
-        <v>819</v>
+        <v>2</v>
+      </c>
+      <c r="E522" s="3"/>
+      <c r="G522" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="H522" s="1" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10894,11 +10930,10 @@
         <v>28</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="G523" s="3"/>
-      <c r="L523" s="1" t="s">
-        <v>727</v>
+        <v>823</v>
+      </c>
+      <c r="G523" s="3" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10909,11 +10944,11 @@
         <v>28</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="G524" s="3"/>
       <c r="L524" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10924,25 +10959,26 @@
         <v>28</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="G525" s="3"/>
       <c r="L525" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A526" s="1" t="s">
+      <c r="A526" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B526" s="1" t="s">
+      <c r="B526" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="I526" s="1" t="s">
-        <v>80</v>
+        <v>735</v>
+      </c>
+      <c r="G526" s="3"/>
+      <c r="L526" s="1" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10953,24 +10989,24 @@
         <v>28</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="J527" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="I527" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A528" s="3" t="s">
+      <c r="A528" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B528" s="3" t="s">
+      <c r="B528" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="G528" s="3" t="s">
-        <v>823</v>
+        <v>826</v>
+      </c>
+      <c r="J528" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10981,10 +11017,10 @@
         <v>28</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="G529" s="3" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10995,35 +11031,38 @@
         <v>28</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="G530" s="3" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A531" s="1" t="s">
+      <c r="A531" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B531" s="1" t="s">
+      <c r="B531" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="J531" s="1" t="s">
-        <v>829</v>
+        <v>831</v>
+      </c>
+      <c r="G531" s="3" t="s">
+        <v>832</v>
       </c>
     </row>
     <row r="532" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A532" s="3" t="s">
+      <c r="A532" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B532" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E532" s="3" t="s">
-        <v>830</v>
+      <c r="B532" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D532" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="J532" s="1" t="s">
+        <v>834</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11034,7 +11073,7 @@
         <v>28</v>
       </c>
       <c r="E533" s="3" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11045,7 +11084,7 @@
         <v>28</v>
       </c>
       <c r="E534" s="3" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11056,7 +11095,7 @@
         <v>28</v>
       </c>
       <c r="E535" s="3" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11067,7 +11106,7 @@
         <v>28</v>
       </c>
       <c r="E536" s="3" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11078,7 +11117,7 @@
         <v>28</v>
       </c>
       <c r="E537" s="3" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11089,7 +11128,7 @@
         <v>28</v>
       </c>
       <c r="E538" s="3" t="s">
-        <v>1</v>
+        <v>840</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11100,7 +11139,7 @@
         <v>28</v>
       </c>
       <c r="E539" s="3" t="s">
-        <v>836</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11110,12 +11149,8 @@
       <c r="B540" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D540" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="E540" s="3"/>
-      <c r="M540" s="1" t="s">
-        <v>838</v>
+      <c r="E540" s="3" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11126,122 +11161,123 @@
         <v>28</v>
       </c>
       <c r="D541" s="1" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E541" s="3"/>
       <c r="M541" s="1" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="542" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="3" t="s">
-        <v>841</v>
+        <v>193</v>
       </c>
       <c r="B542" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="E542" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
+      </c>
+      <c r="E542" s="3"/>
+      <c r="M542" s="1" t="s">
+        <v>845</v>
       </c>
     </row>
     <row r="543" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="3" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="B543" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="E543" s="3" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="544" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="3" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="B544" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="E544" s="3" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="545" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="3" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="B545" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="D545" s="1" t="s">
+        <v>851</v>
+      </c>
       <c r="E545" s="3" t="s">
-        <v>830</v>
+        <v>852</v>
       </c>
     </row>
     <row r="546" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="3" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="B546" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E546" s="3" t="s">
-        <v>94</v>
+        <v>835</v>
       </c>
     </row>
     <row r="547" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D547" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="G547" s="3" t="s">
-        <v>850</v>
+        <v>28</v>
+      </c>
+      <c r="E547" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H548" s="1" t="s">
-        <v>133</v>
+        <v>854</v>
+      </c>
+      <c r="G548" s="3" t="s">
+        <v>855</v>
       </c>
     </row>
     <row r="549" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C549" s="1" t="s">
-        <v>164</v>
+        <v>28</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>723</v>
+        <v>132</v>
+      </c>
+      <c r="H549" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="550" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B550" s="3" t="s">
         <v>34</v>
@@ -11250,12 +11286,12 @@
         <v>164</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>743</v>
+        <v>728</v>
       </c>
     </row>
     <row r="551" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B551" s="3" t="s">
         <v>34</v>
@@ -11264,12 +11300,12 @@
         <v>164</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
     </row>
     <row r="552" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B552" s="3" t="s">
         <v>34</v>
@@ -11278,15 +11314,12 @@
         <v>164</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="G552" s="3" t="s">
-        <v>145</v>
+        <v>745</v>
       </c>
     </row>
     <row r="553" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B553" s="3" t="s">
         <v>34</v>
@@ -11295,7 +11328,7 @@
         <v>164</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="G553" s="3" t="s">
         <v>145</v>
@@ -11303,7 +11336,7 @@
     </row>
     <row r="554" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B554" s="3" t="s">
         <v>34</v>
@@ -11312,7 +11345,7 @@
         <v>164</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="G554" s="3" t="s">
         <v>145</v>
@@ -11320,7 +11353,7 @@
     </row>
     <row r="555" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B555" s="3" t="s">
         <v>34</v>
@@ -11329,12 +11362,15 @@
         <v>164</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>746</v>
+        <v>858</v>
+      </c>
+      <c r="G555" s="3" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B556" s="3" t="s">
         <v>34</v>
@@ -11343,15 +11379,12 @@
         <v>164</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="G556" s="3" t="s">
-        <v>145</v>
+        <v>751</v>
       </c>
     </row>
     <row r="557" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B557" s="3" t="s">
         <v>34</v>
@@ -11360,7 +11393,7 @@
         <v>164</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="G557" s="3" t="s">
         <v>145</v>
@@ -11368,32 +11401,35 @@
     </row>
     <row r="558" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="3" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+      <c r="C558" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="D558" s="1" t="s">
-        <v>857</v>
+        <v>860</v>
+      </c>
+      <c r="G558" s="3" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="559" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="3" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C559" s="1" t="s">
-        <v>164</v>
+        <v>28</v>
       </c>
       <c r="D559" s="1" t="s">
-        <v>723</v>
+        <v>862</v>
       </c>
     </row>
     <row r="560" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="3" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="B560" s="3" t="s">
         <v>34</v>
@@ -11402,15 +11438,12 @@
         <v>164</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="H560" s="1" t="s">
-        <v>145</v>
+        <v>728</v>
       </c>
     </row>
     <row r="561" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="3" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="B561" s="3" t="s">
         <v>34</v>
@@ -11419,12 +11452,15 @@
         <v>164</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>743</v>
+        <v>746</v>
+      </c>
+      <c r="H561" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="562" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="3" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="B562" s="3" t="s">
         <v>34</v>
@@ -11433,12 +11469,12 @@
         <v>164</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="3" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="B563" s="3" t="s">
         <v>34</v>
@@ -11447,45 +11483,59 @@
         <v>164</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="H563" s="1" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
     </row>
     <row r="564" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="3" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B564" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+      <c r="C564" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="D564" s="1" t="s">
-        <v>860</v>
+        <v>863</v>
+      </c>
+      <c r="H564" s="1" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="565" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="3" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B565" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>137</v>
+        <v>865</v>
       </c>
     </row>
     <row r="566" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="3" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="B566" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="G566" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="567" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A567" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D567" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="G567" s="3" t="s">
         <v>96</v>
       </c>
     </row>
